--- a/OFV_Verktoy.xlsx
+++ b/OFV_Verktoy.xlsx
@@ -538,9 +538,9 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
     <col width="17" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
@@ -628,29 +628,21 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>SelgerEierKommune</t>
+          <t>KjoperEierType</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>SelgerBrukerFylke</t>
+          <t>KjoperEierFirma</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>KjoperEierType</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>KjoperEierFirma</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
           <t>Status</t>
         </is>
       </c>
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
